--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487468_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487468_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3944</v>
+        <v>6.9257</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6491</v>
+        <v>3.9132</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7453</v>
+        <v>3.0126</v>
       </c>
       <c r="G2" t="n">
         <v>4.3338</v>
@@ -610,13 +610,13 @@
         <v>1.7626</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1364</v>
+        <v>0.3949</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1494</v>
+        <v>0.1147</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0129</v>
+        <v>0.2803</v>
       </c>
       <c r="V2" t="n">
         <v>0.8260999999999999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>P. SANJURJO BOTEJARA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2715</v>
+        <v>2.5844</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6665</v>
+        <v>0.9853</v>
       </c>
       <c r="F3" t="n">
-        <v>4.9379</v>
+        <v>1.5991</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3545</v>
+        <v>4.2932</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9748</v>
+        <v>2.439</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3797</v>
+        <v>1.8543</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6453</v>
+        <v>4.2089</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1499</v>
+        <v>2.9108</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4954</v>
+        <v>1.2981</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.0843</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8249</v>
+        <v>-0.4718</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1157</v>
+        <v>0.5562</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.546</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.2879</v>
+        <v>-3.1336</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7419</v>
+        <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5206</v>
+        <v>-0.3379</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0338</v>
+        <v>-0.09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4868</v>
+        <v>-0.2479</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0576</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0576</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. SANJURJO BOTEJARA</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7448</v>
+        <v>2.4033</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9853</v>
+        <v>-1.7328</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7595</v>
+        <v>4.136</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2932</v>
+        <v>3.3545</v>
       </c>
       <c r="H4" t="n">
-        <v>2.439</v>
+        <v>1.9748</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8543</v>
+        <v>1.3797</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2089</v>
+        <v>2.6453</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9108</v>
+        <v>1.1499</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2981</v>
+        <v>1.4954</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0843</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4718</v>
+        <v>0.8249</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5562</v>
+        <v>-0.1157</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.3709</v>
+        <v>-2.546</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1336</v>
+        <v>-5.2879</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7626</v>
+        <v>2.7419</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1775</v>
+        <v>1.6524</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.09</v>
+        <v>0.9675</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.08749999999999999</v>
+        <v>0.6849</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6646</v>
+        <v>1.0123</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5625</v>
+        <v>1.8032</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8979</v>
+        <v>-0.7909</v>
       </c>
       <c r="G5" t="n">
         <v>2.7963</v>
@@ -844,13 +844,13 @@
         <v>1.9585</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.1364</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2921</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5033</v>
+        <v>-0.3964</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9412</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0572</v>
+        <v>0.7056</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.339</v>
+        <v>-1.8702</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2818</v>
+        <v>2.5758</v>
       </c>
       <c r="G6" t="n">
         <v>3.35</v>
@@ -922,13 +922,13 @@
         <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0144</v>
+        <v>-0.2516</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7722</v>
+        <v>-0.3035</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2421</v>
+        <v>0.0519</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8260999999999999</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3211</v>
+        <v>-1.0349</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.6728</v>
+        <v>-3.3064</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3517</v>
+        <v>2.2715</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9046</v>
@@ -1000,13 +1000,13 @@
         <v>2.7419</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0052</v>
+        <v>0.281</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1317</v>
+        <v>0.2347</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1265</v>
+        <v>0.0463</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9988</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6071</v>
+        <v>-1.3802</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4441</v>
+        <v>-0.1371</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1629</v>
+        <v>-1.2431</v>
       </c>
       <c r="G8" t="n">
         <v>0.2113</v>
@@ -1078,13 +1078,13 @@
         <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0653</v>
+        <v>0.2922</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2841</v>
+        <v>0.5911</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2187</v>
+        <v>-0.2989</v>
       </c>
       <c r="V8" t="n">
         <v>-1.492</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.9605</v>
+        <v>-5.7897</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.7096</v>
+        <v>-6.9932</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7491</v>
+        <v>1.2036</v>
       </c>
       <c r="G9" t="n">
         <v>-4.9092</v>
@@ -1156,13 +1156,13 @@
         <v>2.3502</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3474</v>
+        <v>-0.1766</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1317</v>
+        <v>0.5846</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2156</v>
+        <v>-0.7612</v>
       </c>
       <c r="V9" t="n">
         <v>0.2754</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>5.129400000000002</v>
+        <v>5.426499999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.635100000000001</v>
+        <v>-7.338000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>12.7645</v>
+        <v>12.7646</v>
       </c>
       <c r="G10" t="n">
         <v>12.5253</v>
@@ -1204,7 +1204,7 @@
         <v>5.124600000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>7.400899999999998</v>
+        <v>7.4009</v>
       </c>
       <c r="J10" t="n">
         <v>11.3486</v>
@@ -1234,10 +1234,10 @@
         <v>16.6471</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6938</v>
+        <v>1.9908</v>
       </c>
       <c r="T10" t="n">
-        <v>2.335</v>
+        <v>2.6319</v>
       </c>
       <c r="U10" t="n">
         <v>-0.641</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. GUERRA TRUJILLO</t>
+          <t>M. ALVAREZ HERNAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4408</v>
+        <v>2.3271</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0752</v>
+        <v>0.5321</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3657</v>
+        <v>1.795</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0427</v>
+        <v>-0.2236</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5836</v>
+        <v>0.2106</v>
       </c>
       <c r="I11" t="n">
-        <v>0.541</v>
+        <v>-0.4342</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6292</v>
+        <v>1.9785</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0223</v>
+        <v>1.3626</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6515</v>
+        <v>0.6159</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6718</v>
+        <v>-2.2021</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5613</v>
+        <v>-1.152</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1105</v>
+        <v>-1.0501</v>
       </c>
       <c r="P11" t="n">
-        <v>2.9377</v>
+        <v>0.5875</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1751</v>
+        <v>-3.1336</v>
       </c>
       <c r="R11" t="n">
-        <v>4.1128</v>
+        <v>3.7211</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2128</v>
+        <v>-0.1947</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0128</v>
+        <v>0.1953</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8</v>
+        <v>-0.3899</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3329</v>
+        <v>2.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6083</v>
+        <v>1.492</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2754</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. ALVAREZ HERNAN</t>
+          <t>D. GUERRA TRUJILLO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.0884</v>
+        <v>2.226</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4298</v>
+        <v>0.5635</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6586</v>
+        <v>1.6625</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2236</v>
+        <v>-1.0427</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2106</v>
+        <v>-1.5836</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4342</v>
+        <v>0.541</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9785</v>
+        <v>0.6292</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3626</v>
+        <v>-0.0223</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6159</v>
+        <v>0.6515</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2021</v>
+        <v>-1.6718</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.152</v>
+        <v>-1.5613</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0501</v>
+        <v>-0.1105</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5875</v>
+        <v>2.9377</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1336</v>
+        <v>-1.1751</v>
       </c>
       <c r="R12" t="n">
-        <v>3.7211</v>
+        <v>4.1128</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4335</v>
+        <v>-0.0021</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0929</v>
+        <v>0.5011</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5264</v>
+        <v>-0.5031</v>
       </c>
       <c r="V12" t="n">
-        <v>2.1578</v>
+        <v>0.3329</v>
       </c>
       <c r="W12" t="n">
-        <v>1.492</v>
+        <v>0.6083</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6659</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. LOPEZ MOURE</t>
+          <t>M. TRAORE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.036</v>
+        <v>1.1538</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3414</v>
+        <v>-0.7533</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6946</v>
+        <v>1.9071</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.5057</v>
+        <v>-0.4417</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5662</v>
+        <v>0.6848</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.0719</v>
+        <v>-1.1264</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2391</v>
+        <v>0.8813</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7672</v>
+        <v>0.9524</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.0063</v>
+        <v>-0.0712</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2667</v>
+        <v>-1.3229</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.201</v>
+        <v>-0.2677</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0656</v>
+        <v>-1.0552</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1751</v>
+        <v>-3.1336</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1543</v>
+        <v>3.3294</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8954</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5378</v>
+        <v>0.007</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3577</v>
+        <v>-0.0994</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3329</v>
+        <v>1.492</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2178</v>
+        <v>1.492</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. TRAORE</t>
+          <t>M. PEREIRA NIETO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2964</v>
+        <v>-0.2253</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.3673</v>
+        <v>-1.0235</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6637</v>
+        <v>0.7982</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4417</v>
+        <v>-0.6558</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6848</v>
+        <v>-0.2364</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.1264</v>
+        <v>-0.4194</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8813</v>
+        <v>0.4098</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9524</v>
+        <v>0.4406</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0712</v>
+        <v>-0.0308</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3229</v>
+        <v>-1.0656</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2677</v>
+        <v>-0.677</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0552</v>
+        <v>-0.3886</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1958</v>
+        <v>1.7626</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1336</v>
+        <v>-0.9792</v>
       </c>
       <c r="R14" t="n">
-        <v>3.3294</v>
+        <v>2.7419</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9497</v>
+        <v>-0.5061</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.607</v>
+        <v>-0.454</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3428</v>
+        <v>-0.052</v>
       </c>
       <c r="V14" t="n">
-        <v>1.492</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. PEREIRA NIETO</t>
+          <t>D. LOPEZ MOURE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4605</v>
+        <v>-0.8124</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.7398</v>
+        <v>-1.296</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2793</v>
+        <v>0.4836</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6558</v>
+        <v>-2.5057</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2364</v>
+        <v>0.5662</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4194</v>
+        <v>-3.0719</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4098</v>
+        <v>-1.2391</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4406</v>
+        <v>0.7672</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0308</v>
+        <v>-2.0063</v>
       </c>
       <c r="M15" t="n">
+        <v>-1.2667</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.201</v>
+      </c>
+      <c r="O15" t="n">
         <v>-1.0656</v>
       </c>
-      <c r="N15" t="n">
-        <v>-0.677</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-0.3886</v>
-      </c>
       <c r="P15" t="n">
-        <v>1.7626</v>
+        <v>0.9792</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9792</v>
+        <v>-1.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7419</v>
+        <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7413</v>
+        <v>1.047</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1704</v>
+        <v>0.9004</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4291</v>
+        <v>0.1466</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.3329</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.2178</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.7559</v>
+        <v>-1.6803</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0315</v>
+        <v>-0.9291</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7244</v>
+        <v>-0.7512</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1104</v>
@@ -1702,13 +1702,13 @@
         <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4866</v>
+        <v>-0.411</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.22</v>
+        <v>-0.1176</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2666</v>
+        <v>-0.2933</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5507</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.9543</v>
+        <v>-2.6159</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.7477</v>
+        <v>-2.543</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2066</v>
+        <v>-0.073</v>
       </c>
       <c r="G17" t="n">
         <v>-2.1588</v>
@@ -1780,13 +1780,13 @@
         <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5996</v>
+        <v>-0.2613</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4158</v>
+        <v>-0.2111</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1838</v>
+        <v>-0.0501</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.8204</v>
+        <v>-4.8201</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.7245</v>
+        <v>-7.3151</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9041</v>
+        <v>2.495</v>
       </c>
       <c r="G18" t="n">
         <v>-4.3868</v>
@@ -1858,13 +1858,13 @@
         <v>4.3087</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5914</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5893</v>
+        <v>-0.18</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0021</v>
+        <v>-0.4112</v>
       </c>
       <c r="V18" t="n">
         <v>0.9412</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.1295</v>
+        <v>-4.447099999999999</v>
       </c>
       <c r="E19" t="n">
         <v>-12.7644</v>
       </c>
       <c r="F19" t="n">
-        <v>7.635</v>
+        <v>8.317200000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-12.5255</v>
@@ -1927,7 +1927,7 @@
         <v>-5.2503</v>
       </c>
       <c r="P19" t="n">
-        <v>5.875299999999999</v>
+        <v>5.8753</v>
       </c>
       <c r="Q19" t="n">
         <v>-16.6471</v>
@@ -1936,13 +1936,13 @@
         <v>22.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6939</v>
+        <v>-1.0117</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6409999999999996</v>
+        <v>0.6411</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.3349</v>
+        <v>-1.6524</v>
       </c>
       <c r="V19" t="n">
         <v>3.2142</v>
